--- a/Amator_Telsizcilik_Tablo_A_Mevzuat_Envanteri_v1.0.xlsx
+++ b/Amator_Telsizcilik_Tablo_A_Mevzuat_Envanteri_v1.0.xlsx
@@ -3024,7 +3024,7 @@
     <row r="11" ht="90" customHeight="1" s="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>GA-RX</t>
+          <t>GA-RX/Kanal</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>dernek ve kulüpler ve kulüpler: Hafıza programlama disiplini konusunda üye bilgilendirmesi. Pratik öneri: Cihaz hafızası yalnızca amatör/yayıncılık bantlarını içermeli; askerî/güvenlik frekansları kaydedilmemeli. SDR preset dosyaları aynı dikkatle yönetilmeli.</t>
+          <t>Dernek ve kulüpler: Hafıza programlama disiplini konusunda üye bilgilendirmesi. Pratik öneri: Cihaz hafızası yalnızca amatör/yayıncılık bantlarını içermeli; askerî/güvenlik frekansları kaydedilmemeli. SDR preset dosyaları aynı dikkatle yönetilmeli. Ayrıca BTK ve Adalet Bakanlığı'na, kanal/tarama hafızasının olağan teknik özellik olduğu ve salt frekans kaydının başlı başına suç kastı göstermediği yönünde teknik açıklama/delil takdiri talebi (Tablo B Taslak 12).</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">

--- a/Amator_Telsizcilik_Tablo_A_Mevzuat_Envanteri_v1.0.xlsx
+++ b/Amator_Telsizcilik_Tablo_A_Mevzuat_Envanteri_v1.0.xlsx
@@ -3762,17 +3762,17 @@
       </c>
       <c r="C25" s="22" t="inlineStr">
         <is>
-          <t>Vefat/iptal sonrası 10 yıl pasif; in-memoriam vesayet</t>
+          <t>Md.7/2 vesayet mekanizması; süre sonrası akıbet ve eşdeğer belge şartı</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
         <is>
-          <t>KEGM Yönetmeliği, belge iptalinde (vefat dâhil) çağrı işaretini 10 yıl pasif tutar ve başkasına vermez/devredilemez. SK'nın resmî tanımı, 10 yıl sonrası akıbet ve aileye/kulübe 'in memoriam' vesayet yolu tanımsızdır. 'Babadan oğla geçme' fiilî bir talep olup hukuki dayanağı yoktur; bekleyeni almak isteyenler ile koruma/vesayet isteyenler arasında gerginlik vardır.</t>
+          <t>KEGM Yönetmeliği Md.7, vefatı 10 yıllık bekletme hükmünün (fıkra 1) kapsamı DIŞINDA tutar; fıkra 2 ayrı bir hüküm olarak, belgenin geçerlilik süresi içinde olmak, aynı bölgede ikamet etmek ve eşdeğer belgeye sahip olmak kaydıyla çağrı işaretinin varis/vasiye tahsis edilebileceğini düzenler. Yani 'vesayet yolu tanımsız/hukuki dayanaksız' algısı isabetli değildir; ancak mekanizma dardır: süre sonrası akıbet belirsiz, belgesiz aile üyeleri kapsam dışı, tahsis KEGM takdirinde.</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
         <is>
-          <t>KEGM Sınav ve Belgelendirme Yönetmeliği (RG 27482): belge iptali sonrası çağrı işareti 10 yıl yeniden tahsis edilmez; devredilemez.</t>
+          <t>KEGM Sınav ve Belgelendirme Yönetmeliği (RG 27482) Md.7/1 (10 yıl bekletme; vefat hariç) ve Md.7/2 (vefat/vesayette şartlı varis/vasi tahsisi).</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H25" s="22" t="inlineStr">
         <is>
-          <t>KEGM'den: (1) SK ve çağrı işareti yaşam döngüsünün tanımlanması; (2) bekletme süresinin (koru/uzat/kısalt/kaldır) ve vesayetin (devredilemez / şartlı aile-kulüp / süre sonu serbest / kalıcı anıt) usule bağlanması.</t>
+          <t>KEGM'den: (1) Md.7/2'nin belge süresi sonrası akıbetinin netleştirilmesi; (2) 'eşdeğer belge sahibi olma' şartının esnetilip esnetilemeyeceğinin değerlendirilmesi; (3) mekanizmanın topluluğa rehberle duyurulması.</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">

--- a/Amator_Telsizcilik_Tablo_A_Mevzuat_Envanteri_v1.0.xlsx
+++ b/Amator_Telsizcilik_Tablo_A_Mevzuat_Envanteri_v1.0.xlsx
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Afet Haberleşmesi: AFAD ile Resmî Protokol (MOU)</t>
+          <t>Afet Haberleşmesinde Amatörün Rolü: Tanım ve Kapsam</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>KEGM Yön. Md.4/1e afet haberleşmesini amatör istasyon amacı sayar; ancak AFAD ile amatörleri kapsayan resmî protokol yok. Katkı plansız kalıyor; 'depremde lazım olur' söylemi istismara açık; kamu yararı kurumsal kayda bağlanmamış.</t>
+          <t>KEGM Yön. Md.4/1e afet haberleşmesini amatör istasyon amacı sayar; FTM Teknik Ölçütler Md.22 §3-§4 afette yardım ve izinli kurum frekansı kullanımına dayanak verir. TAMP ana metninde amatör dernekleri ismen yok (genel 'STK' kategorisi); ancak Ulusal Düzey Afet Haberleşme Grubu Planı yazışmalarında (2012, 2015, 2024) TRAC ismen 'çözüm ortağı'. Boşluk: görev içeriği kamuya açık değil; bireysel amatör tanımsız; 2000 protokolünün güncelliği teyit edilemiyor.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>AFAD + KEGM/BTK: ulusal MOU; il AFAD-kulüp eşleşmesi; afet planlarında amatör frekans/rolleri</t>
+          <t>AFAD + Ulaştırma ve Altyapı Bak. + KEGM/BTK: planın amatörlere ilişkin bölümünün açıklanması; görev tanımının (teknik destek/malzeme/operatörlük) netleştirilmesi; bireysel amatörün dâhil olma usulü; il eşleşmesi ve tatbikat; 2000 protokolünün güncellik teyidi</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>UYGULANMIYOR — TR'de AFAD/AKUT/Sahil Güvenlik ile amatörleri kapsayan resmi bir EMCOMM protokolü veya MOU bulunmamaktadır.</t>
+          <t>KISMÎ — TRAC, ulusal afet haberleşme planı yazışmalarında ismen 'çözüm ortağı' olarak anılıyor; ancak IARU ETG'nin öngördüğü türden, görev içeriği tanımlı ve kamuya açık bir iş birliği belgesi bulunmuyor.</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
